--- a/samples/3_cabling_shuffle_invalid.xlsx
+++ b/samples/3_cabling_shuffle_invalid.xlsx
@@ -423,13 +423,13 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="28" customWidth="1" min="13" max="13"/>
@@ -550,7 +550,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lab1-dh1-r01-spine01:swp1</t>
+          <t>swp1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -572,7 +572,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>lab1-dh1-r01-leaf01:swp9</t>
+          <t>swp9</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -652,7 +652,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>lab1-dh1-r02-leaf01:swp9</t>
+          <t>swp9</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>swp2s0</t>
+          <t>swp1s0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lab1-dh1-r01-leaf01:swp2</t>
+          <t>swp2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -708,7 +708,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>lab1-dh1-r01-leaf01:swp9</t>
+          <t>swp9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
